--- a/ASCal/bin/Debug/Fluke_114.xlsx
+++ b/ASCal/bin/Debug/Fluke_114.xlsx
@@ -5981,23 +5981,23 @@
       <c r="J73" s="192"/>
       <c r="K73" s="192"/>
       <c r="L73" s="192"/>
-      <c r="M73" s="192" t="str">
+      <c r="M73" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM52,"0.0")," ",DataSheet!P52)</f>
-        <v>0.0 Ω</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N73" s="192"/>
       <c r="O73" s="192"/>
       <c r="P73" s="192"/>
-      <c r="Q73" s="192" t="str">
+      <c r="Q73" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR52,"0.0")," ",DataSheet!P52)</f>
-        <v>0.0 Ω</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R73" s="192"/>
       <c r="S73" s="192"/>
       <c r="T73" s="192"/>
-      <c r="U73" s="192" t="str">
+      <c r="U73" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE52,"0.000")," ",DataSheet!DF52)</f>
-        <v>0.058 Ω</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V73" s="192"/>
       <c r="W73" s="192"/>
@@ -6017,23 +6017,23 @@
       <c r="J74" s="192"/>
       <c r="K74" s="192"/>
       <c r="L74" s="192"/>
-      <c r="M74" s="192" t="str">
+      <c r="M74" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM53,"0.0")," ",DataSheet!P53)</f>
-        <v>500.0 Ω</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N74" s="192"/>
       <c r="O74" s="192"/>
       <c r="P74" s="192"/>
-      <c r="Q74" s="192" t="str">
+      <c r="Q74" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR53,"0.0")," ",DataSheet!P53)</f>
-        <v>0.0 Ω</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R74" s="192"/>
       <c r="S74" s="192"/>
       <c r="T74" s="192"/>
-      <c r="U74" s="192" t="str">
+      <c r="U74" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE53,"0.000")," ",DataSheet!DF53)</f>
-        <v>0.058 Ω</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V74" s="192"/>
       <c r="W74" s="192"/>
@@ -6056,23 +6056,23 @@
       <c r="J75" s="192"/>
       <c r="K75" s="192"/>
       <c r="L75" s="192"/>
-      <c r="M75" s="192" t="str">
+      <c r="M75" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM54,"0.000")," ",DataSheet!P54)</f>
-        <v>5.000 kΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N75" s="192"/>
       <c r="O75" s="192"/>
       <c r="P75" s="192"/>
-      <c r="Q75" s="192" t="str">
+      <c r="Q75" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR54,"0.000")," ",DataSheet!P54)</f>
-        <v>0.000 kΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R75" s="192"/>
       <c r="S75" s="192"/>
       <c r="T75" s="192"/>
-      <c r="U75" s="192" t="str">
+      <c r="U75" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE54,"0.000\ 00")," ",DataSheet!DF54)</f>
-        <v>0.000 58 kΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V75" s="192"/>
       <c r="W75" s="192"/>
@@ -6095,23 +6095,23 @@
       <c r="J76" s="192"/>
       <c r="K76" s="192"/>
       <c r="L76" s="192"/>
-      <c r="M76" s="192" t="str">
+      <c r="M76" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM55,"0.00")," ",DataSheet!P55)</f>
-        <v>50.00 kΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N76" s="192"/>
       <c r="O76" s="192"/>
       <c r="P76" s="192"/>
-      <c r="Q76" s="192" t="str">
+      <c r="Q76" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR55,"0.00")," ",DataSheet!P55)</f>
-        <v>0.00 kΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R76" s="192"/>
       <c r="S76" s="192"/>
       <c r="T76" s="192"/>
-      <c r="U76" s="192" t="str">
+      <c r="U76" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE55,"0.000\ 0")," ",DataSheet!DF55)</f>
-        <v>0.005 8 kΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V76" s="192"/>
       <c r="W76" s="192"/>
@@ -6134,23 +6134,23 @@
       <c r="J77" s="192"/>
       <c r="K77" s="192"/>
       <c r="L77" s="192"/>
-      <c r="M77" s="192" t="str">
+      <c r="M77" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM56,"0.0")," ",DataSheet!P56)</f>
-        <v>500.0 kΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N77" s="192"/>
       <c r="O77" s="192"/>
       <c r="P77" s="192"/>
-      <c r="Q77" s="192" t="str">
+      <c r="Q77" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR56,"0.0")," ",DataSheet!P56)</f>
-        <v>0.0 kΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R77" s="192"/>
       <c r="S77" s="192"/>
       <c r="T77" s="192"/>
-      <c r="U77" s="192" t="str">
+      <c r="U77" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE56,"0.000")," ",DataSheet!DF56)</f>
-        <v>0.058 kΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V77" s="192"/>
       <c r="W77" s="192"/>
@@ -6173,23 +6173,23 @@
       <c r="J78" s="192"/>
       <c r="K78" s="192"/>
       <c r="L78" s="192"/>
-      <c r="M78" s="192" t="str">
+      <c r="M78" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM57,"0.000")," ",DataSheet!P57)</f>
-        <v>5.000 MΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N78" s="192"/>
       <c r="O78" s="192"/>
       <c r="P78" s="192"/>
-      <c r="Q78" s="192" t="str">
+      <c r="Q78" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR57,"0.000")," ",DataSheet!P57)</f>
-        <v>0.000 MΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R78" s="192"/>
       <c r="S78" s="192"/>
       <c r="T78" s="192"/>
-      <c r="U78" s="192" t="str">
+      <c r="U78" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE57,"0.000\ 00")," ",DataSheet!DF57)</f>
-        <v>0.000 80 MΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V78" s="192"/>
       <c r="W78" s="192"/>
@@ -6212,23 +6212,23 @@
       <c r="J79" s="192"/>
       <c r="K79" s="192"/>
       <c r="L79" s="192"/>
-      <c r="M79" s="192" t="str">
+      <c r="M79" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM58,"0.00")," ",DataSheet!P58)</f>
-        <v>10.00 MΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N79" s="192"/>
       <c r="O79" s="192"/>
       <c r="P79" s="192"/>
-      <c r="Q79" s="192" t="str">
+      <c r="Q79" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR58,"0.00")," ",DataSheet!P58)</f>
-        <v>0.00 MΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R79" s="192"/>
       <c r="S79" s="192"/>
       <c r="T79" s="192"/>
-      <c r="U79" s="192" t="str">
+      <c r="U79" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE58,"0.000\ 0")," ",DataSheet!DF58)</f>
-        <v>0.005 8 MΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V79" s="192"/>
       <c r="W79" s="192"/>
@@ -6248,23 +6248,23 @@
       <c r="J80" s="192"/>
       <c r="K80" s="192"/>
       <c r="L80" s="192"/>
-      <c r="M80" s="192" t="str">
+      <c r="M80" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM59,"0.00")," ",DataSheet!P59)</f>
-        <v>30.00 MΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N80" s="192"/>
       <c r="O80" s="192"/>
       <c r="P80" s="192"/>
-      <c r="Q80" s="192" t="str">
+      <c r="Q80" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR59,"0.00")," ",DataSheet!P59)</f>
-        <v>0.00 MΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R80" s="192"/>
       <c r="S80" s="192"/>
       <c r="T80" s="192"/>
-      <c r="U80" s="192" t="str">
+      <c r="U80" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE59,"0.000\ 0")," ",DataSheet!DF59)</f>
-        <v>0.005 9 MΩ</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V80" s="192"/>
       <c r="W80" s="192"/>
@@ -6658,21 +6658,21 @@
       <c r="L93" s="192"/>
       <c r="M93" s="192" t="str">
         <f>CONCATENATE(DataSheet!AH70," ",DataSheet!P70)</f>
-        <v>5 V</v>
+        <v xml:space="preserve"> V</v>
       </c>
       <c r="N93" s="192"/>
       <c r="O93" s="192"/>
       <c r="P93" s="192"/>
-      <c r="Q93" s="192" t="str">
+      <c r="Q93" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR70,"0.000")," ",DataSheet!P70)</f>
-        <v>0.000 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R93" s="192"/>
       <c r="S93" s="192"/>
       <c r="T93" s="192"/>
-      <c r="U93" s="192" t="str">
+      <c r="U93" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE70,"0.000\ 0")," ",DataSheet!DF70)</f>
-        <v>0.007 3 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V93" s="192"/>
       <c r="W93" s="192"/>
@@ -6694,21 +6694,21 @@
       <c r="L94" s="192"/>
       <c r="M94" s="192" t="str">
         <f>CONCATENATE(DataSheet!AH71," ",DataSheet!P71)</f>
-        <v>5 V</v>
+        <v xml:space="preserve"> V</v>
       </c>
       <c r="N94" s="192"/>
       <c r="O94" s="192"/>
       <c r="P94" s="192"/>
-      <c r="Q94" s="192" t="str">
+      <c r="Q94" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR71,"0.000")," ",DataSheet!P71)</f>
-        <v>0.000 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R94" s="192"/>
       <c r="S94" s="192"/>
       <c r="T94" s="192"/>
-      <c r="U94" s="192" t="str">
+      <c r="U94" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE71,"0.000\ 0")," ",DataSheet!DF71)</f>
-        <v>0.007 3 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V94" s="192"/>
       <c r="W94" s="192"/>
@@ -6733,21 +6733,21 @@
       <c r="L95" s="192"/>
       <c r="M95" s="192" t="str">
         <f>CONCATENATE(DataSheet!AH72," ",DataSheet!P72)</f>
-        <v>50 V</v>
+        <v xml:space="preserve"> V</v>
       </c>
       <c r="N95" s="192"/>
       <c r="O95" s="192"/>
       <c r="P95" s="192"/>
-      <c r="Q95" s="192" t="str">
+      <c r="Q95" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR72,"0.00")," ",DataSheet!P72)</f>
-        <v>0.00 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R95" s="192"/>
       <c r="S95" s="192"/>
       <c r="T95" s="192"/>
-      <c r="U95" s="192" t="str">
+      <c r="U95" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE72,"0.000")," ",DataSheet!DF72)</f>
-        <v>0.071 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V95" s="192"/>
       <c r="W95" s="192"/>
@@ -6769,21 +6769,21 @@
       <c r="L96" s="192"/>
       <c r="M96" s="192" t="str">
         <f>CONCATENATE(DataSheet!AH73," ",DataSheet!P73)</f>
-        <v>50 V</v>
+        <v xml:space="preserve"> V</v>
       </c>
       <c r="N96" s="192"/>
       <c r="O96" s="192"/>
       <c r="P96" s="192"/>
-      <c r="Q96" s="192" t="str">
+      <c r="Q96" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR73,"0.00")," ",DataSheet!P73)</f>
-        <v>0.00 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R96" s="192"/>
       <c r="S96" s="192"/>
       <c r="T96" s="192"/>
-      <c r="U96" s="192" t="str">
+      <c r="U96" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE73,"0.000")," ",DataSheet!DF73)</f>
-        <v>0.071 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V96" s="192"/>
       <c r="W96" s="192"/>
@@ -6808,21 +6808,21 @@
       <c r="L97" s="192"/>
       <c r="M97" s="192" t="str">
         <f>CONCATENATE(DataSheet!AH74," ",DataSheet!P74)</f>
-        <v>600 V</v>
+        <v xml:space="preserve"> V</v>
       </c>
       <c r="N97" s="192"/>
       <c r="O97" s="192"/>
       <c r="P97" s="192"/>
-      <c r="Q97" s="192" t="str">
+      <c r="Q97" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR74,"0.0")," ",DataSheet!P74)</f>
-        <v>0.0 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R97" s="192"/>
       <c r="S97" s="192"/>
       <c r="T97" s="192"/>
-      <c r="U97" s="192" t="str">
+      <c r="U97" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE74,"0.000")," ",DataSheet!DF74)</f>
-        <v>0.092 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V97" s="192"/>
       <c r="W97" s="192"/>
@@ -6844,21 +6844,21 @@
       <c r="L98" s="192"/>
       <c r="M98" s="192" t="str">
         <f>CONCATENATE(DataSheet!AH75," ",DataSheet!P75)</f>
-        <v>600 V</v>
+        <v xml:space="preserve"> V</v>
       </c>
       <c r="N98" s="192"/>
       <c r="O98" s="192"/>
       <c r="P98" s="192"/>
-      <c r="Q98" s="192" t="str">
+      <c r="Q98" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR75,"0.0")," ",DataSheet!P75)</f>
-        <v>0.0 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R98" s="192"/>
       <c r="S98" s="192"/>
       <c r="T98" s="192"/>
-      <c r="U98" s="192" t="str">
+      <c r="U98" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE75,"0.000")," ",DataSheet!DF75)</f>
-        <v>0.092 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V98" s="192"/>
       <c r="W98" s="192"/>
@@ -6994,23 +6994,23 @@
       <c r="J104" s="192"/>
       <c r="K104" s="192"/>
       <c r="L104" s="192"/>
-      <c r="M104" s="192" t="str">
+      <c r="M104" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM81,"0.000")," ",DataSheet!P81)</f>
-        <v>0.000 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N104" s="192"/>
       <c r="O104" s="192"/>
       <c r="P104" s="192"/>
-      <c r="Q104" s="192" t="str">
+      <c r="Q104" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR81,"0.000")," ",DataSheet!P81)</f>
-        <v>0.000 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R104" s="192"/>
       <c r="S104" s="192"/>
       <c r="T104" s="192"/>
-      <c r="U104" s="192" t="str">
+      <c r="U104" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE81,"0.000\ 00")," ",DataSheet!DF81)</f>
-        <v>0.000 58 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V104" s="192"/>
       <c r="W104" s="192"/>
@@ -7030,23 +7030,23 @@
       <c r="J105" s="192"/>
       <c r="K105" s="192"/>
       <c r="L105" s="192"/>
-      <c r="M105" s="192" t="str">
+      <c r="M105" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM82,"0.000")," ",DataSheet!P82)</f>
-        <v>5.000 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N105" s="192"/>
       <c r="O105" s="192"/>
       <c r="P105" s="192"/>
-      <c r="Q105" s="192" t="str">
+      <c r="Q105" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR82,"0.000")," ",DataSheet!P82)</f>
-        <v>0.000 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R105" s="192"/>
       <c r="S105" s="192"/>
       <c r="T105" s="192"/>
-      <c r="U105" s="192" t="str">
+      <c r="U105" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE82,"0.000\ 00")," ",DataSheet!DF82)</f>
-        <v>0.000 58 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V105" s="192"/>
       <c r="W105" s="192"/>
@@ -7069,23 +7069,23 @@
       <c r="J106" s="192"/>
       <c r="K106" s="192"/>
       <c r="L106" s="192"/>
-      <c r="M106" s="192" t="str">
+      <c r="M106" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM83,"0.00")," ",DataSheet!P83)</f>
-        <v>50.00 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N106" s="192"/>
       <c r="O106" s="192"/>
       <c r="P106" s="192"/>
-      <c r="Q106" s="192" t="str">
+      <c r="Q106" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR83,"0.00")," ",DataSheet!P83)</f>
-        <v>0.00 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R106" s="192"/>
       <c r="S106" s="192"/>
       <c r="T106" s="192"/>
-      <c r="U106" s="192" t="str">
+      <c r="U106" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE83,"0.000\ 0")," ",DataSheet!DF83)</f>
-        <v>0.005 8 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V106" s="192"/>
       <c r="W106" s="192"/>
@@ -7108,23 +7108,23 @@
       <c r="J107" s="192"/>
       <c r="K107" s="192"/>
       <c r="L107" s="192"/>
-      <c r="M107" s="192" t="str">
+      <c r="M107" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM84,"0.0")," ",DataSheet!P84)</f>
-        <v>600.0 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N107" s="192"/>
       <c r="O107" s="192"/>
       <c r="P107" s="192"/>
-      <c r="Q107" s="192" t="str">
+      <c r="Q107" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR84,"0.0")," ",DataSheet!P84)</f>
-        <v>0.0 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R107" s="192"/>
       <c r="S107" s="192"/>
       <c r="T107" s="192"/>
-      <c r="U107" s="192" t="str">
+      <c r="U107" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE84,"0.000")," ",DataSheet!DF84)</f>
-        <v>0.058 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V107" s="192"/>
       <c r="W107" s="192"/>
@@ -7144,23 +7144,23 @@
       <c r="J108" s="192"/>
       <c r="K108" s="192"/>
       <c r="L108" s="192"/>
-      <c r="M108" s="192" t="str">
+      <c r="M108" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM85,"0.0")," ",DataSheet!P85)</f>
-        <v>-600.0 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N108" s="192"/>
       <c r="O108" s="192"/>
       <c r="P108" s="192"/>
-      <c r="Q108" s="192" t="str">
+      <c r="Q108" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR85,"0.0")," ",DataSheet!P85)</f>
-        <v>0.0 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R108" s="192"/>
       <c r="S108" s="192"/>
       <c r="T108" s="192"/>
-      <c r="U108" s="192" t="str">
+      <c r="U108" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE85,"0.000")," ",DataSheet!DF85)</f>
-        <v>0.058 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V108" s="192"/>
       <c r="W108" s="192"/>
@@ -7600,23 +7600,23 @@
       <c r="J134" s="192"/>
       <c r="K134" s="192"/>
       <c r="L134" s="192"/>
-      <c r="M134" s="192" t="str">
+      <c r="M134" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM96,"0.0")," ",DataSheet!P96)</f>
-        <v>10.0 mV</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N134" s="192"/>
       <c r="O134" s="192"/>
       <c r="P134" s="192"/>
-      <c r="Q134" s="192" t="str">
+      <c r="Q134" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR96,"0.0")," ",DataSheet!P96)</f>
-        <v>0.0 mV</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R134" s="192"/>
       <c r="S134" s="192"/>
       <c r="T134" s="192"/>
-      <c r="U134" s="192" t="str">
+      <c r="U134" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE96,"0.000")," ",DataSheet!DF96)</f>
-        <v>0.058 mV</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V134" s="192"/>
       <c r="W134" s="192"/>
@@ -7637,23 +7637,23 @@
       <c r="J135" s="192"/>
       <c r="K135" s="192"/>
       <c r="L135" s="192"/>
-      <c r="M135" s="192" t="str">
+      <c r="M135" s="192" t="e">
         <f>CONCATENATE(DataSheet!AM97," ",DataSheet!P97)</f>
-        <v>600 mV</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N135" s="192"/>
       <c r="O135" s="192"/>
       <c r="P135" s="192"/>
-      <c r="Q135" s="192" t="str">
+      <c r="Q135" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR97,"0.0")," ",DataSheet!P97)</f>
-        <v>0.0 mV</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R135" s="192"/>
       <c r="S135" s="192"/>
       <c r="T135" s="192"/>
-      <c r="U135" s="192" t="str">
+      <c r="U135" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE97,"0.000")," ",DataSheet!DF97)</f>
-        <v>0.058 mV</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V135" s="192"/>
       <c r="W135" s="192"/>
@@ -7777,23 +7777,23 @@
       <c r="J141" s="192"/>
       <c r="K141" s="192"/>
       <c r="L141" s="192"/>
-      <c r="M141" s="192" t="str">
+      <c r="M141" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM102,"0.0")," ",DataSheet!P102)</f>
-        <v>0.5 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N141" s="192"/>
       <c r="O141" s="192"/>
       <c r="P141" s="192"/>
-      <c r="Q141" s="192" t="str">
+      <c r="Q141" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR102,"0.0")," ",DataSheet!P102)</f>
-        <v>0.0 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R141" s="192"/>
       <c r="S141" s="192"/>
       <c r="T141" s="192"/>
-      <c r="U141" s="192" t="str">
+      <c r="U141" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE102,"0.000")," ",DataSheet!DF102)</f>
-        <v>0.058 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V141" s="192"/>
       <c r="W141" s="192"/>
@@ -7814,23 +7814,23 @@
       <c r="J142" s="192"/>
       <c r="K142" s="192"/>
       <c r="L142" s="192"/>
-      <c r="M142" s="192" t="str">
+      <c r="M142" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM103,"0.0")," ",DataSheet!P103)</f>
-        <v>0.5 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N142" s="192"/>
       <c r="O142" s="192"/>
       <c r="P142" s="192"/>
-      <c r="Q142" s="192" t="str">
+      <c r="Q142" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR103,"0.0")," ",DataSheet!P103)</f>
-        <v>0.0 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R142" s="192"/>
       <c r="S142" s="192"/>
       <c r="T142" s="192"/>
-      <c r="U142" s="192" t="str">
+      <c r="U142" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE103,"0.000")," ",DataSheet!DF103)</f>
-        <v>0.058 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V142" s="192"/>
       <c r="W142" s="192"/>
@@ -7851,23 +7851,23 @@
       <c r="J143" s="192"/>
       <c r="K143" s="192"/>
       <c r="L143" s="192"/>
-      <c r="M143" s="192" t="str">
+      <c r="M143" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AM104,"0.0")," ",DataSheet!P104)</f>
-        <v>500.0 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N143" s="192"/>
       <c r="O143" s="192"/>
       <c r="P143" s="192"/>
-      <c r="Q143" s="192" t="str">
+      <c r="Q143" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!AR104,"0.0")," ",DataSheet!P104)</f>
-        <v>0.0 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R143" s="192"/>
       <c r="S143" s="192"/>
       <c r="T143" s="192"/>
-      <c r="U143" s="192" t="str">
+      <c r="U143" s="192" t="e">
         <f>CONCATENATE(TEXT(DataSheet!DE104,"0.000")," ",DataSheet!DF104)</f>
-        <v>0.092 V</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V143" s="192"/>
       <c r="W143" s="192"/>
@@ -13706,38 +13706,32 @@
       <c r="U52" s="257"/>
       <c r="V52" s="257"/>
       <c r="W52" s="257"/>
-      <c r="X52" s="245">
-        <v>0</v>
-      </c>
+      <c r="X52" s="245"/>
       <c r="Y52" s="245"/>
       <c r="Z52" s="245"/>
       <c r="AA52" s="245"/>
       <c r="AB52" s="245"/>
-      <c r="AC52" s="245">
-        <v>0</v>
-      </c>
+      <c r="AC52" s="245"/>
       <c r="AD52" s="245"/>
       <c r="AE52" s="245"/>
       <c r="AF52" s="245"/>
       <c r="AG52" s="245"/>
-      <c r="AH52" s="245">
-        <v>0</v>
-      </c>
+      <c r="AH52" s="245"/>
       <c r="AI52" s="245"/>
       <c r="AJ52" s="245"/>
       <c r="AK52" s="245"/>
       <c r="AL52" s="245"/>
-      <c r="AM52" s="245">
+      <c r="AM52" s="245" t="e">
         <f>ROUND(AVERAGE(X52:AL52),1)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN52" s="257"/>
       <c r="AO52" s="257"/>
       <c r="AP52" s="257"/>
       <c r="AQ52" s="257"/>
-      <c r="AR52" s="245">
+      <c r="AR52" s="245" t="e">
         <f>AM52-L52</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS52" s="257"/>
       <c r="AT52" s="257"/>
@@ -13770,9 +13764,9 @@
       <c r="BN52" s="245"/>
       <c r="BO52" s="245"/>
       <c r="BP52" s="245"/>
-      <c r="BQ52" s="246" t="str">
+      <c r="BQ52" s="246" t="e">
         <f t="shared" ref="BQ52:BQ59" si="0">IF(AND(AM52&lt;=BG52,AM52&gt;=BL52),"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR52" s="246"/>
       <c r="BS52" s="246"/>
@@ -13838,9 +13832,9 @@
       <c r="CP52" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="CQ52" s="64">
+      <c r="CQ52" s="64" t="e">
         <f>_xlfn.STDEV.P(X52:AL52)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR52" s="65" t="str">
         <f t="shared" ref="CR52:CR59" si="7">P52</f>
@@ -13850,26 +13844,26 @@
         <f>SQRT(3)</f>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT52" s="68">
+      <c r="CT52" s="68" t="e">
         <f t="shared" ref="CT52:CT58" si="8">CQ52/CS52</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU52" s="9"/>
-      <c r="CV52" s="78">
+      <c r="CV52" s="78" t="e">
         <f>SQRT(SUMSQ(CT52,CN52,CH52,CB52))</f>
-        <v>2.8867539132792972E-2</v>
-      </c>
-      <c r="CW52" s="79">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW52" s="79" t="e">
         <f>(CV52^4)/(((CT52^4)/2)+((CN52^4)/200)+((CH52^4)/200)+((CB52^4)/200))</f>
-        <v>200.00071148000006</v>
-      </c>
-      <c r="CX52" s="83">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX52" s="83" t="e">
         <f t="shared" ref="CX52:CX58" si="9">ROUND(TINV(0.05,CW52),0)</f>
-        <v>2</v>
-      </c>
-      <c r="CY52" s="92">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY52" s="92" t="e">
         <f>ROUND((CV52*CX52),3)</f>
-        <v>5.8000000000000003E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ52" s="80" t="str">
         <f t="shared" ref="CZ52:CZ59" si="10">P52</f>
@@ -13884,9 +13878,9 @@
         <v>Ω</v>
       </c>
       <c r="DD52" s="136"/>
-      <c r="DE52" s="137">
+      <c r="DE52" s="137" t="e">
         <f>MAX(CY52:DB52)</f>
-        <v>5.8000000000000003E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF52" s="138" t="str">
         <f>CZ52</f>
@@ -13925,38 +13919,32 @@
       <c r="U53" s="257"/>
       <c r="V53" s="257"/>
       <c r="W53" s="257"/>
-      <c r="X53" s="245">
-        <v>500</v>
-      </c>
+      <c r="X53" s="245"/>
       <c r="Y53" s="245"/>
       <c r="Z53" s="245"/>
       <c r="AA53" s="245"/>
       <c r="AB53" s="245"/>
-      <c r="AC53" s="245">
-        <v>500</v>
-      </c>
+      <c r="AC53" s="245"/>
       <c r="AD53" s="245"/>
       <c r="AE53" s="245"/>
       <c r="AF53" s="245"/>
       <c r="AG53" s="245"/>
-      <c r="AH53" s="245">
-        <v>500</v>
-      </c>
+      <c r="AH53" s="245"/>
       <c r="AI53" s="245"/>
       <c r="AJ53" s="245"/>
       <c r="AK53" s="245"/>
       <c r="AL53" s="245"/>
-      <c r="AM53" s="245">
+      <c r="AM53" s="245" t="e">
         <f>ROUND(AVERAGE(X53:AL53),1)</f>
-        <v>500</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN53" s="257"/>
       <c r="AO53" s="257"/>
       <c r="AP53" s="257"/>
       <c r="AQ53" s="257"/>
-      <c r="AR53" s="245">
+      <c r="AR53" s="245" t="e">
         <f t="shared" ref="AR53:AR58" si="11">AM53-L53</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS53" s="257"/>
       <c r="AT53" s="257"/>
@@ -13989,9 +13977,9 @@
       <c r="BN53" s="254"/>
       <c r="BO53" s="254"/>
       <c r="BP53" s="255"/>
-      <c r="BQ53" s="246" t="str">
+      <c r="BQ53" s="246" t="e">
         <f t="shared" si="0"/>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR53" s="246"/>
       <c r="BS53" s="246"/>
@@ -14057,9 +14045,9 @@
       <c r="CP53" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="CQ53" s="8">
+      <c r="CQ53" s="8" t="e">
         <f t="shared" ref="CQ53:CQ59" si="14">_xlfn.STDEV.P(X53:AL53)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR53" s="7" t="str">
         <f t="shared" si="7"/>
@@ -14069,26 +14057,26 @@
         <f t="shared" ref="CS53:CS59" si="15">SQRT(3)</f>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT53" s="69">
+      <c r="CT53" s="69" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU53" s="9"/>
-      <c r="CV53" s="73">
+      <c r="CV53" s="73" t="e">
         <f t="shared" ref="CV53:CV59" si="16">SQRT(SUMSQ(CT53,CN53,CH53,CB53))</f>
-        <v>2.8906458332582589E-2</v>
-      </c>
-      <c r="CW53" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW53" s="10" t="e">
         <f t="shared" ref="CW53:CW59" si="17">(CV53^4)/(((CT53^4)/2)+((CN53^4)/200)+((CH53^4)/200)+((CB53^4)/200))</f>
-        <v>201.07999212685738</v>
-      </c>
-      <c r="CX53" s="84">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX53" s="84" t="e">
         <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="CY53" s="91">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY53" s="91" t="e">
         <f>ROUND((CV53*CX53),5)</f>
-        <v>5.781E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ53" s="74" t="str">
         <f t="shared" si="10"/>
@@ -14103,9 +14091,9 @@
         <v>Ω</v>
       </c>
       <c r="DD53" s="136"/>
-      <c r="DE53" s="141">
+      <c r="DE53" s="141" t="e">
         <f t="shared" ref="DE53:DE59" si="19">MAX(CY53:DB53)</f>
-        <v>5.781E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF53" s="142" t="str">
         <f t="shared" ref="DF53:DF59" si="20">CZ53</f>
@@ -14144,38 +14132,32 @@
       <c r="U54" s="257"/>
       <c r="V54" s="257"/>
       <c r="W54" s="257"/>
-      <c r="X54" s="252">
-        <v>5</v>
-      </c>
+      <c r="X54" s="252"/>
       <c r="Y54" s="252"/>
       <c r="Z54" s="252"/>
       <c r="AA54" s="252"/>
       <c r="AB54" s="252"/>
-      <c r="AC54" s="252">
-        <v>5</v>
-      </c>
+      <c r="AC54" s="252"/>
       <c r="AD54" s="252"/>
       <c r="AE54" s="252"/>
       <c r="AF54" s="252"/>
       <c r="AG54" s="252"/>
-      <c r="AH54" s="252">
-        <v>5</v>
-      </c>
+      <c r="AH54" s="252"/>
       <c r="AI54" s="252"/>
       <c r="AJ54" s="252"/>
       <c r="AK54" s="252"/>
       <c r="AL54" s="252"/>
-      <c r="AM54" s="252">
+      <c r="AM54" s="252" t="e">
         <f>ROUND(AVERAGE(X54:AL54),3)</f>
-        <v>5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN54" s="252"/>
       <c r="AO54" s="252"/>
       <c r="AP54" s="252"/>
       <c r="AQ54" s="252"/>
-      <c r="AR54" s="252">
+      <c r="AR54" s="252" t="e">
         <f>AM54-L54</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS54" s="252"/>
       <c r="AT54" s="252"/>
@@ -14208,9 +14190,9 @@
       <c r="BN54" s="362"/>
       <c r="BO54" s="362"/>
       <c r="BP54" s="363"/>
-      <c r="BQ54" s="246" t="str">
+      <c r="BQ54" s="246" t="e">
         <f t="shared" si="0"/>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR54" s="246"/>
       <c r="BS54" s="246"/>
@@ -14276,9 +14258,9 @@
       <c r="CP54" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="CQ54" s="8">
+      <c r="CQ54" s="8" t="e">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR54" s="7" t="str">
         <f t="shared" si="7"/>
@@ -14288,26 +14270,26 @@
         <f t="shared" si="15"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT54" s="69">
+      <c r="CT54" s="69" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU54" s="9"/>
-      <c r="CV54" s="73">
+      <c r="CV54" s="73" t="e">
         <f t="shared" si="16"/>
-        <v>2.899820396737242E-4</v>
-      </c>
-      <c r="CW54" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW54" s="10" t="e">
         <f t="shared" si="17"/>
-        <v>203.62970107369958</v>
-      </c>
-      <c r="CX54" s="84">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX54" s="84" t="e">
         <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="CY54" s="91">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY54" s="91" t="e">
         <f>ROUND((CV54*CX54),5)</f>
-        <v>5.8E-4</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ54" s="74" t="str">
         <f t="shared" si="10"/>
@@ -14322,9 +14304,9 @@
         <v>kΩ</v>
       </c>
       <c r="DD54" s="136"/>
-      <c r="DE54" s="141">
+      <c r="DE54" s="141" t="e">
         <f t="shared" si="19"/>
-        <v>5.8E-4</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF54" s="142" t="str">
         <f t="shared" si="20"/>
@@ -14363,38 +14345,32 @@
       <c r="U55" s="257"/>
       <c r="V55" s="257"/>
       <c r="W55" s="257"/>
-      <c r="X55" s="256">
-        <v>50</v>
-      </c>
+      <c r="X55" s="256"/>
       <c r="Y55" s="256"/>
       <c r="Z55" s="256"/>
       <c r="AA55" s="256"/>
       <c r="AB55" s="256"/>
-      <c r="AC55" s="256">
-        <v>50</v>
-      </c>
+      <c r="AC55" s="256"/>
       <c r="AD55" s="256"/>
       <c r="AE55" s="256"/>
       <c r="AF55" s="256"/>
       <c r="AG55" s="256"/>
-      <c r="AH55" s="256">
-        <v>50</v>
-      </c>
+      <c r="AH55" s="256"/>
       <c r="AI55" s="256"/>
       <c r="AJ55" s="256"/>
       <c r="AK55" s="256"/>
       <c r="AL55" s="256"/>
-      <c r="AM55" s="256">
+      <c r="AM55" s="256" t="e">
         <f>ROUND(AVERAGE(X55:AL55),2)</f>
-        <v>50</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN55" s="256"/>
       <c r="AO55" s="256"/>
       <c r="AP55" s="256"/>
       <c r="AQ55" s="256"/>
-      <c r="AR55" s="256">
+      <c r="AR55" s="256" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS55" s="256"/>
       <c r="AT55" s="256"/>
@@ -14427,9 +14403,9 @@
       <c r="BN55" s="259"/>
       <c r="BO55" s="259"/>
       <c r="BP55" s="260"/>
-      <c r="BQ55" s="246" t="str">
+      <c r="BQ55" s="246" t="e">
         <f t="shared" si="0"/>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR55" s="246"/>
       <c r="BS55" s="246"/>
@@ -14495,9 +14471,9 @@
       <c r="CP55" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="CQ55" s="8">
+      <c r="CQ55" s="8" t="e">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR55" s="7" t="str">
         <f t="shared" si="7"/>
@@ -14507,26 +14483,26 @@
         <f t="shared" si="15"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT55" s="69">
+      <c r="CT55" s="69" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU55" s="9"/>
-      <c r="CV55" s="73">
+      <c r="CV55" s="73" t="e">
         <f t="shared" si="16"/>
-        <v>2.9150228701218337E-3</v>
-      </c>
-      <c r="CW55" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW55" s="10" t="e">
         <f t="shared" si="17"/>
-        <v>207.8701509422734</v>
-      </c>
-      <c r="CX55" s="84">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX55" s="84" t="e">
         <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="CY55" s="87">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY55" s="87" t="e">
         <f>ROUND((CV55*CX55),4)</f>
-        <v>5.7999999999999996E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ55" s="74" t="str">
         <f t="shared" si="10"/>
@@ -14541,9 +14517,9 @@
         <v>kΩ</v>
       </c>
       <c r="DD55" s="136"/>
-      <c r="DE55" s="141">
+      <c r="DE55" s="141" t="e">
         <f t="shared" si="19"/>
-        <v>5.7999999999999996E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF55" s="142" t="str">
         <f t="shared" si="20"/>
@@ -14582,38 +14558,32 @@
       <c r="U56" s="257"/>
       <c r="V56" s="257"/>
       <c r="W56" s="257"/>
-      <c r="X56" s="245">
-        <v>500</v>
-      </c>
+      <c r="X56" s="245"/>
       <c r="Y56" s="245"/>
       <c r="Z56" s="245"/>
       <c r="AA56" s="245"/>
       <c r="AB56" s="245"/>
-      <c r="AC56" s="245">
-        <v>500</v>
-      </c>
+      <c r="AC56" s="245"/>
       <c r="AD56" s="245"/>
       <c r="AE56" s="245"/>
       <c r="AF56" s="245"/>
       <c r="AG56" s="245"/>
-      <c r="AH56" s="245">
-        <v>500</v>
-      </c>
+      <c r="AH56" s="245"/>
       <c r="AI56" s="245"/>
       <c r="AJ56" s="245"/>
       <c r="AK56" s="245"/>
       <c r="AL56" s="245"/>
-      <c r="AM56" s="245">
+      <c r="AM56" s="245" t="e">
         <f>ROUND(AVERAGE(X56:AL56),1)</f>
-        <v>500</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN56" s="257"/>
       <c r="AO56" s="257"/>
       <c r="AP56" s="257"/>
       <c r="AQ56" s="257"/>
-      <c r="AR56" s="245">
+      <c r="AR56" s="245" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS56" s="257"/>
       <c r="AT56" s="257"/>
@@ -14646,9 +14616,9 @@
       <c r="BN56" s="254"/>
       <c r="BO56" s="254"/>
       <c r="BP56" s="255"/>
-      <c r="BQ56" s="246" t="str">
+      <c r="BQ56" s="246" t="e">
         <f t="shared" si="0"/>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR56" s="246"/>
       <c r="BS56" s="246"/>
@@ -14714,9 +14684,9 @@
       <c r="CP56" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="CQ56" s="8">
+      <c r="CQ56" s="8" t="e">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR56" s="7" t="str">
         <f t="shared" si="7"/>
@@ -14726,26 +14696,26 @@
         <f t="shared" si="15"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT56" s="69">
+      <c r="CT56" s="69" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU56" s="9"/>
-      <c r="CV56" s="73">
+      <c r="CV56" s="73" t="e">
         <f t="shared" si="16"/>
-        <v>2.9055521563608758E-2</v>
-      </c>
-      <c r="CW56" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW56" s="10" t="e">
         <f t="shared" si="17"/>
-        <v>205.22630748975618</v>
-      </c>
-      <c r="CX56" s="84">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX56" s="84" t="e">
         <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="CY56" s="87">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY56" s="87" t="e">
         <f>ROUND((CV56*CX56),4)</f>
-        <v>5.8099999999999999E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ56" s="74" t="str">
         <f t="shared" si="10"/>
@@ -14760,9 +14730,9 @@
         <v>kΩ</v>
       </c>
       <c r="DD56" s="136"/>
-      <c r="DE56" s="141">
+      <c r="DE56" s="141" t="e">
         <f t="shared" si="19"/>
-        <v>5.8099999999999999E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF56" s="142" t="str">
         <f t="shared" si="20"/>
@@ -14801,38 +14771,32 @@
       <c r="U57" s="257"/>
       <c r="V57" s="257"/>
       <c r="W57" s="257"/>
-      <c r="X57" s="252">
-        <v>5</v>
-      </c>
+      <c r="X57" s="252"/>
       <c r="Y57" s="252"/>
       <c r="Z57" s="252"/>
       <c r="AA57" s="252"/>
       <c r="AB57" s="252"/>
-      <c r="AC57" s="252">
-        <v>5</v>
-      </c>
+      <c r="AC57" s="252"/>
       <c r="AD57" s="252"/>
       <c r="AE57" s="252"/>
       <c r="AF57" s="252"/>
       <c r="AG57" s="252"/>
-      <c r="AH57" s="252">
-        <v>5</v>
-      </c>
+      <c r="AH57" s="252"/>
       <c r="AI57" s="252"/>
       <c r="AJ57" s="252"/>
       <c r="AK57" s="252"/>
       <c r="AL57" s="252"/>
-      <c r="AM57" s="252">
+      <c r="AM57" s="252" t="e">
         <f>ROUND(AVERAGE(X57:AL57),3)</f>
-        <v>5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN57" s="252"/>
       <c r="AO57" s="252"/>
       <c r="AP57" s="252"/>
       <c r="AQ57" s="252"/>
-      <c r="AR57" s="252">
+      <c r="AR57" s="252" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS57" s="252"/>
       <c r="AT57" s="252"/>
@@ -14865,9 +14829,9 @@
       <c r="BN57" s="362"/>
       <c r="BO57" s="362"/>
       <c r="BP57" s="363"/>
-      <c r="BQ57" s="246" t="str">
+      <c r="BQ57" s="246" t="e">
         <f t="shared" si="0"/>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR57" s="246"/>
       <c r="BS57" s="246"/>
@@ -14933,9 +14897,9 @@
       <c r="CP57" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="CQ57" s="8">
+      <c r="CQ57" s="8" t="e">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR57" s="7" t="str">
         <f t="shared" si="7"/>
@@ -14945,26 +14909,26 @@
         <f t="shared" si="15"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT57" s="69">
+      <c r="CT57" s="69" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU57" s="9"/>
-      <c r="CV57" s="73">
+      <c r="CV57" s="73" t="e">
         <f t="shared" si="16"/>
-        <v>3.75410886008029E-4</v>
-      </c>
-      <c r="CW57" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW57" s="10" t="e">
         <f t="shared" si="17"/>
-        <v>387.09430419108577</v>
-      </c>
-      <c r="CX57" s="84">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX57" s="84" t="e">
         <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="CY57" s="87">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY57" s="87" t="e">
         <f>ROUND((CV57*CX57),4)</f>
-        <v>8.0000000000000004E-4</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ57" s="74" t="str">
         <f t="shared" si="10"/>
@@ -14979,9 +14943,9 @@
         <v>MΩ</v>
       </c>
       <c r="DD57" s="136"/>
-      <c r="DE57" s="141">
+      <c r="DE57" s="141" t="e">
         <f t="shared" si="19"/>
-        <v>8.0000000000000004E-4</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF57" s="142" t="str">
         <f t="shared" si="20"/>
@@ -15020,38 +14984,32 @@
       <c r="U58" s="257"/>
       <c r="V58" s="257"/>
       <c r="W58" s="257"/>
-      <c r="X58" s="256">
-        <v>10</v>
-      </c>
+      <c r="X58" s="256"/>
       <c r="Y58" s="256"/>
       <c r="Z58" s="256"/>
       <c r="AA58" s="256"/>
       <c r="AB58" s="256"/>
-      <c r="AC58" s="256">
-        <v>10</v>
-      </c>
+      <c r="AC58" s="256"/>
       <c r="AD58" s="256"/>
       <c r="AE58" s="256"/>
       <c r="AF58" s="256"/>
       <c r="AG58" s="256"/>
-      <c r="AH58" s="256">
-        <v>10</v>
-      </c>
+      <c r="AH58" s="256"/>
       <c r="AI58" s="256"/>
       <c r="AJ58" s="256"/>
       <c r="AK58" s="256"/>
       <c r="AL58" s="256"/>
-      <c r="AM58" s="256">
+      <c r="AM58" s="256" t="e">
         <f t="shared" ref="AM58" si="21">ROUND(AVERAGE(X58:AL58),2)</f>
-        <v>10</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN58" s="256"/>
       <c r="AO58" s="256"/>
       <c r="AP58" s="256"/>
       <c r="AQ58" s="256"/>
-      <c r="AR58" s="256">
+      <c r="AR58" s="256" t="e">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS58" s="256"/>
       <c r="AT58" s="256"/>
@@ -15084,9 +15042,9 @@
       <c r="BN58" s="259"/>
       <c r="BO58" s="259"/>
       <c r="BP58" s="260"/>
-      <c r="BQ58" s="246" t="str">
+      <c r="BQ58" s="246" t="e">
         <f t="shared" si="0"/>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR58" s="246"/>
       <c r="BS58" s="246"/>
@@ -15152,9 +15110,9 @@
       <c r="CP58" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="CQ58" s="8">
+      <c r="CQ58" s="8" t="e">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR58" s="7" t="str">
         <f t="shared" si="7"/>
@@ -15164,26 +15122,26 @@
         <f t="shared" si="15"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT58" s="69">
+      <c r="CT58" s="69" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU58" s="9"/>
-      <c r="CV58" s="73">
+      <c r="CV58" s="73" t="e">
         <f t="shared" si="16"/>
-        <v>2.8967107783369282E-3</v>
-      </c>
-      <c r="CW58" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW58" s="10" t="e">
         <f t="shared" si="17"/>
-        <v>202.7646679159333</v>
-      </c>
-      <c r="CX58" s="84">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX58" s="84" t="e">
         <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="CY58" s="87">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY58" s="87" t="e">
         <f t="shared" ref="CY58:CY59" si="22">ROUND((CV58*CX58),4)</f>
-        <v>5.7999999999999996E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ58" s="74" t="str">
         <f t="shared" si="10"/>
@@ -15198,9 +15156,9 @@
         <v>MΩ</v>
       </c>
       <c r="DD58" s="136"/>
-      <c r="DE58" s="141">
+      <c r="DE58" s="141" t="e">
         <f t="shared" si="19"/>
-        <v>5.7999999999999996E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF58" s="142" t="str">
         <f t="shared" si="20"/>
@@ -15237,38 +15195,32 @@
       <c r="U59" s="257"/>
       <c r="V59" s="257"/>
       <c r="W59" s="257"/>
-      <c r="X59" s="256">
-        <v>30</v>
-      </c>
+      <c r="X59" s="256"/>
       <c r="Y59" s="256"/>
       <c r="Z59" s="256"/>
       <c r="AA59" s="256"/>
       <c r="AB59" s="256"/>
-      <c r="AC59" s="256">
-        <v>30</v>
-      </c>
+      <c r="AC59" s="256"/>
       <c r="AD59" s="256"/>
       <c r="AE59" s="256"/>
       <c r="AF59" s="256"/>
       <c r="AG59" s="256"/>
-      <c r="AH59" s="256">
-        <v>30</v>
-      </c>
+      <c r="AH59" s="256"/>
       <c r="AI59" s="256"/>
       <c r="AJ59" s="256"/>
       <c r="AK59" s="256"/>
       <c r="AL59" s="256"/>
-      <c r="AM59" s="256">
+      <c r="AM59" s="256" t="e">
         <f t="shared" ref="AM59" si="23">ROUND(AVERAGE(X59:AL59),2)</f>
-        <v>30</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN59" s="256"/>
       <c r="AO59" s="256"/>
       <c r="AP59" s="256"/>
       <c r="AQ59" s="256"/>
-      <c r="AR59" s="256">
+      <c r="AR59" s="256" t="e">
         <f t="shared" ref="AR59" si="24">AM59-L59</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS59" s="256"/>
       <c r="AT59" s="256"/>
@@ -15301,9 +15253,9 @@
       <c r="BN59" s="259"/>
       <c r="BO59" s="259"/>
       <c r="BP59" s="260"/>
-      <c r="BQ59" s="246" t="str">
+      <c r="BQ59" s="246" t="e">
         <f t="shared" si="0"/>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR59" s="246"/>
       <c r="BS59" s="246"/>
@@ -15369,9 +15321,9 @@
       <c r="CP59" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="CQ59" s="66">
+      <c r="CQ59" s="66" t="e">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR59" s="53" t="str">
         <f t="shared" si="7"/>
@@ -15381,26 +15333,26 @@
         <f t="shared" si="15"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT59" s="70">
+      <c r="CT59" s="70" t="e">
         <f t="shared" ref="CT59" si="27">CQ59/CS59</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU59" s="9"/>
-      <c r="CV59" s="75">
+      <c r="CV59" s="75" t="e">
         <f t="shared" si="16"/>
-        <v>2.9704096238285611E-3</v>
-      </c>
-      <c r="CW59" s="76">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW59" s="76" t="e">
         <f t="shared" si="17"/>
-        <v>223.43896119799561</v>
-      </c>
-      <c r="CX59" s="85">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX59" s="85" t="e">
         <f t="shared" ref="CX59" si="28">ROUND(TINV(0.05,CW59),0)</f>
-        <v>2</v>
-      </c>
-      <c r="CY59" s="89">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY59" s="89" t="e">
         <f t="shared" si="22"/>
-        <v>5.8999999999999999E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ59" s="77" t="str">
         <f t="shared" si="10"/>
@@ -15415,9 +15367,9 @@
         <v>MΩ</v>
       </c>
       <c r="DD59" s="136"/>
-      <c r="DE59" s="151">
+      <c r="DE59" s="151" t="e">
         <f t="shared" si="19"/>
-        <v>5.8999999999999999E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF59" s="152" t="str">
         <f t="shared" si="20"/>
@@ -16648,38 +16600,32 @@
       <c r="U70" s="257"/>
       <c r="V70" s="257"/>
       <c r="W70" s="257"/>
-      <c r="X70" s="252">
-        <v>5</v>
-      </c>
+      <c r="X70" s="252"/>
       <c r="Y70" s="252"/>
       <c r="Z70" s="252"/>
       <c r="AA70" s="252"/>
       <c r="AB70" s="252"/>
-      <c r="AC70" s="252">
-        <v>5</v>
-      </c>
+      <c r="AC70" s="252"/>
       <c r="AD70" s="252"/>
       <c r="AE70" s="252"/>
       <c r="AF70" s="252"/>
       <c r="AG70" s="252"/>
-      <c r="AH70" s="252">
-        <v>5</v>
-      </c>
+      <c r="AH70" s="252"/>
       <c r="AI70" s="252"/>
       <c r="AJ70" s="252"/>
       <c r="AK70" s="252"/>
       <c r="AL70" s="252"/>
-      <c r="AM70" s="252">
+      <c r="AM70" s="252" t="e">
         <f>ROUND(AVERAGE(X70:AL70),3)</f>
-        <v>5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN70" s="252"/>
       <c r="AO70" s="252"/>
       <c r="AP70" s="252"/>
       <c r="AQ70" s="252"/>
-      <c r="AR70" s="252">
+      <c r="AR70" s="252" t="e">
         <f>AM70-L70</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS70" s="252"/>
       <c r="AT70" s="252"/>
@@ -16712,9 +16658,9 @@
       <c r="BN70" s="252"/>
       <c r="BO70" s="252"/>
       <c r="BP70" s="252"/>
-      <c r="BQ70" s="246" t="str">
+      <c r="BQ70" s="246" t="e">
         <f t="shared" ref="BQ70:BQ75" si="29">IF(AND(AM70&lt;=BG70,AM70&gt;=BL70),"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR70" s="246"/>
       <c r="BS70" s="246"/>
@@ -16780,9 +16726,9 @@
       <c r="CP70" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="CQ70" s="64">
+      <c r="CQ70" s="64" t="e">
         <f t="shared" ref="CQ70:CQ75" si="38">_xlfn.STDEV.P(X70:AL70)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR70" s="65" t="str">
         <f t="shared" ref="CR70:CR75" si="39">P70</f>
@@ -16792,26 +16738,26 @@
         <f t="shared" ref="CS70:CS75" si="40">SQRT(3)</f>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT70" s="68">
+      <c r="CT70" s="68" t="e">
         <f t="shared" ref="CT70" si="41">CQ70/CS70</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU70" s="9"/>
-      <c r="CV70" s="188">
+      <c r="CV70" s="188" t="e">
         <f t="shared" ref="CV70:CV75" si="42">SQRT(SUMSQ(CT70,CN70,CH70,CB70))</f>
-        <v>3.6613977294652563E-3</v>
-      </c>
-      <c r="CW70" s="132">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW70" s="132" t="e">
         <f t="shared" ref="CW70:CW75" si="43">(CV70^4)/(((CT70^4)/2)+((CN70^4)/200)+((CH70^4)/200)+((CB70^4)/200))</f>
-        <v>202.50193501088827</v>
-      </c>
-      <c r="CX70" s="83">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX70" s="83" t="e">
         <f t="shared" ref="CX70" si="44">ROUND(TINV(0.05,CW70),0)</f>
-        <v>2</v>
-      </c>
-      <c r="CY70" s="86">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY70" s="86" t="e">
         <f>ROUND((CV70*CX70),4)</f>
-        <v>7.3000000000000001E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ70" s="80" t="str">
         <f t="shared" ref="CZ70:CZ75" si="45">P70</f>
@@ -16826,9 +16772,9 @@
         <v>V</v>
       </c>
       <c r="DD70" s="136"/>
-      <c r="DE70" s="137">
+      <c r="DE70" s="137" t="e">
         <f>MAX(CY70:DB70)</f>
-        <v>7.3000000000000001E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF70" s="138" t="str">
         <f t="shared" ref="DF70:DF75" si="47">CZ70</f>
@@ -16867,38 +16813,32 @@
       <c r="U71" s="257"/>
       <c r="V71" s="257"/>
       <c r="W71" s="257"/>
-      <c r="X71" s="252">
-        <v>5</v>
-      </c>
+      <c r="X71" s="252"/>
       <c r="Y71" s="252"/>
       <c r="Z71" s="252"/>
       <c r="AA71" s="252"/>
       <c r="AB71" s="252"/>
-      <c r="AC71" s="252">
-        <v>5</v>
-      </c>
+      <c r="AC71" s="252"/>
       <c r="AD71" s="252"/>
       <c r="AE71" s="252"/>
       <c r="AF71" s="252"/>
       <c r="AG71" s="252"/>
-      <c r="AH71" s="252">
-        <v>5</v>
-      </c>
+      <c r="AH71" s="252"/>
       <c r="AI71" s="252"/>
       <c r="AJ71" s="252"/>
       <c r="AK71" s="252"/>
       <c r="AL71" s="252"/>
-      <c r="AM71" s="252">
+      <c r="AM71" s="252" t="e">
         <f>ROUND(AVERAGE(X71:AL71),3)</f>
-        <v>5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN71" s="252"/>
       <c r="AO71" s="252"/>
       <c r="AP71" s="252"/>
       <c r="AQ71" s="252"/>
-      <c r="AR71" s="252">
+      <c r="AR71" s="252" t="e">
         <f t="shared" ref="AR71:AR75" si="48">AM71-L71</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS71" s="252"/>
       <c r="AT71" s="252"/>
@@ -16931,9 +16871,9 @@
       <c r="BN71" s="252"/>
       <c r="BO71" s="252"/>
       <c r="BP71" s="252"/>
-      <c r="BQ71" s="246" t="str">
+      <c r="BQ71" s="246" t="e">
         <f t="shared" si="29"/>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR71" s="246"/>
       <c r="BS71" s="246"/>
@@ -16999,9 +16939,9 @@
       <c r="CP71" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="CQ71" s="8">
+      <c r="CQ71" s="8" t="e">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR71" s="7" t="str">
         <f t="shared" si="39"/>
@@ -17011,26 +16951,26 @@
         <f t="shared" si="40"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT71" s="69">
+      <c r="CT71" s="69" t="e">
         <f t="shared" ref="CT71:CT75" si="51">CQ71/CS71</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU71" s="9"/>
-      <c r="CV71" s="189">
+      <c r="CV71" s="189" t="e">
         <f t="shared" si="42"/>
-        <v>3.6613977294652563E-3</v>
-      </c>
-      <c r="CW71" s="139">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW71" s="139" t="e">
         <f t="shared" si="43"/>
-        <v>202.50193501088827</v>
-      </c>
-      <c r="CX71" s="84">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX71" s="84" t="e">
         <f t="shared" ref="CX71:CX75" si="52">ROUND(TINV(0.05,CW71),0)</f>
-        <v>2</v>
-      </c>
-      <c r="CY71" s="87">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY71" s="87" t="e">
         <f>ROUND((CV71*CX71),4)</f>
-        <v>7.3000000000000001E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ71" s="74" t="str">
         <f t="shared" si="45"/>
@@ -17045,9 +16985,9 @@
         <v>V</v>
       </c>
       <c r="DD71" s="136"/>
-      <c r="DE71" s="141">
+      <c r="DE71" s="141" t="e">
         <f t="shared" ref="DE71:DE75" si="53">IF(CY71&lt;DB71,DB71,CY71)</f>
-        <v>7.3000000000000001E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF71" s="142" t="str">
         <f t="shared" si="47"/>
@@ -17086,38 +17026,32 @@
       <c r="U72" s="257"/>
       <c r="V72" s="257"/>
       <c r="W72" s="257"/>
-      <c r="X72" s="258">
-        <v>50</v>
-      </c>
+      <c r="X72" s="258"/>
       <c r="Y72" s="259"/>
       <c r="Z72" s="259"/>
       <c r="AA72" s="259"/>
       <c r="AB72" s="260"/>
-      <c r="AC72" s="258">
-        <v>50</v>
-      </c>
+      <c r="AC72" s="258"/>
       <c r="AD72" s="259"/>
       <c r="AE72" s="259"/>
       <c r="AF72" s="259"/>
       <c r="AG72" s="260"/>
-      <c r="AH72" s="258">
-        <v>50</v>
-      </c>
+      <c r="AH72" s="258"/>
       <c r="AI72" s="259"/>
       <c r="AJ72" s="259"/>
       <c r="AK72" s="259"/>
       <c r="AL72" s="260"/>
-      <c r="AM72" s="256">
+      <c r="AM72" s="256" t="e">
         <f>ROUND(AVERAGE(X72:AL72),2)</f>
-        <v>50</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN72" s="256"/>
       <c r="AO72" s="256"/>
       <c r="AP72" s="256"/>
       <c r="AQ72" s="256"/>
-      <c r="AR72" s="256">
+      <c r="AR72" s="256" t="e">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS72" s="256"/>
       <c r="AT72" s="256"/>
@@ -17150,9 +17084,9 @@
       <c r="BN72" s="256"/>
       <c r="BO72" s="256"/>
       <c r="BP72" s="256"/>
-      <c r="BQ72" s="246" t="str">
+      <c r="BQ72" s="246" t="e">
         <f t="shared" si="29"/>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR72" s="246"/>
       <c r="BS72" s="246"/>
@@ -17218,9 +17152,9 @@
       <c r="CP72" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="CQ72" s="8">
+      <c r="CQ72" s="8" t="e">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR72" s="7" t="str">
         <f t="shared" si="39"/>
@@ -17230,26 +17164,26 @@
         <f t="shared" si="40"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT72" s="69">
+      <c r="CT72" s="69" t="e">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU72" s="9"/>
-      <c r="CV72" s="189">
+      <c r="CV72" s="189" t="e">
         <f t="shared" si="42"/>
-        <v>3.561717750374576E-2</v>
-      </c>
-      <c r="CW72" s="139">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW72" s="139" t="e">
         <f t="shared" si="43"/>
-        <v>202.64486220323451</v>
-      </c>
-      <c r="CX72" s="84">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX72" s="84" t="e">
         <f t="shared" si="52"/>
-        <v>2</v>
-      </c>
-      <c r="CY72" s="88">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY72" s="88" t="e">
         <f t="shared" ref="CY72:CY73" si="54">ROUND((CV72*CX72),3)</f>
-        <v>7.0999999999999994E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ72" s="74" t="str">
         <f t="shared" si="45"/>
@@ -17264,9 +17198,9 @@
         <v>V</v>
       </c>
       <c r="DD72" s="136"/>
-      <c r="DE72" s="141">
+      <c r="DE72" s="141" t="e">
         <f t="shared" si="53"/>
-        <v>7.0999999999999994E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF72" s="142" t="str">
         <f t="shared" si="47"/>
@@ -17305,38 +17239,32 @@
       <c r="U73" s="257"/>
       <c r="V73" s="257"/>
       <c r="W73" s="257"/>
-      <c r="X73" s="258">
-        <v>50</v>
-      </c>
+      <c r="X73" s="258"/>
       <c r="Y73" s="259"/>
       <c r="Z73" s="259"/>
       <c r="AA73" s="259"/>
       <c r="AB73" s="260"/>
-      <c r="AC73" s="258">
-        <v>50</v>
-      </c>
+      <c r="AC73" s="258"/>
       <c r="AD73" s="259"/>
       <c r="AE73" s="259"/>
       <c r="AF73" s="259"/>
       <c r="AG73" s="260"/>
-      <c r="AH73" s="258">
-        <v>50</v>
-      </c>
+      <c r="AH73" s="258"/>
       <c r="AI73" s="259"/>
       <c r="AJ73" s="259"/>
       <c r="AK73" s="259"/>
       <c r="AL73" s="260"/>
-      <c r="AM73" s="256">
+      <c r="AM73" s="256" t="e">
         <f>ROUND(AVERAGE(X73:AL73),2)</f>
-        <v>50</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN73" s="256"/>
       <c r="AO73" s="256"/>
       <c r="AP73" s="256"/>
       <c r="AQ73" s="256"/>
-      <c r="AR73" s="256">
+      <c r="AR73" s="256" t="e">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS73" s="256"/>
       <c r="AT73" s="256"/>
@@ -17369,9 +17297,9 @@
       <c r="BN73" s="256"/>
       <c r="BO73" s="256"/>
       <c r="BP73" s="256"/>
-      <c r="BQ73" s="246" t="str">
+      <c r="BQ73" s="246" t="e">
         <f t="shared" si="29"/>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR73" s="246"/>
       <c r="BS73" s="246"/>
@@ -17437,9 +17365,9 @@
       <c r="CP73" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="CQ73" s="8">
+      <c r="CQ73" s="8" t="e">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR73" s="7" t="str">
         <f t="shared" si="39"/>
@@ -17449,26 +17377,26 @@
         <f t="shared" si="40"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT73" s="69">
+      <c r="CT73" s="69" t="e">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU73" s="9"/>
-      <c r="CV73" s="189">
+      <c r="CV73" s="189" t="e">
         <f t="shared" si="42"/>
-        <v>3.561717750374576E-2</v>
-      </c>
-      <c r="CW73" s="139">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW73" s="139" t="e">
         <f t="shared" si="43"/>
-        <v>202.64486220323451</v>
-      </c>
-      <c r="CX73" s="84">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX73" s="84" t="e">
         <f t="shared" si="52"/>
-        <v>2</v>
-      </c>
-      <c r="CY73" s="88">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY73" s="88" t="e">
         <f t="shared" si="54"/>
-        <v>7.0999999999999994E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ73" s="74" t="str">
         <f t="shared" si="45"/>
@@ -17483,9 +17411,9 @@
         <v>V</v>
       </c>
       <c r="DD73" s="136"/>
-      <c r="DE73" s="141">
+      <c r="DE73" s="141" t="e">
         <f t="shared" si="53"/>
-        <v>7.0999999999999994E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF73" s="142" t="str">
         <f t="shared" si="47"/>
@@ -17524,38 +17452,32 @@
       <c r="U74" s="257"/>
       <c r="V74" s="257"/>
       <c r="W74" s="257"/>
-      <c r="X74" s="253">
-        <v>600</v>
-      </c>
+      <c r="X74" s="253"/>
       <c r="Y74" s="254"/>
       <c r="Z74" s="254"/>
       <c r="AA74" s="254"/>
       <c r="AB74" s="255"/>
-      <c r="AC74" s="253">
-        <v>600</v>
-      </c>
+      <c r="AC74" s="253"/>
       <c r="AD74" s="254"/>
       <c r="AE74" s="254"/>
       <c r="AF74" s="254"/>
       <c r="AG74" s="255"/>
-      <c r="AH74" s="253">
-        <v>600</v>
-      </c>
+      <c r="AH74" s="253"/>
       <c r="AI74" s="254"/>
       <c r="AJ74" s="254"/>
       <c r="AK74" s="254"/>
       <c r="AL74" s="255"/>
-      <c r="AM74" s="245">
+      <c r="AM74" s="245" t="e">
         <f>ROUND(AVERAGE(X74:AL74),1)</f>
-        <v>600</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN74" s="245"/>
       <c r="AO74" s="245"/>
       <c r="AP74" s="245"/>
       <c r="AQ74" s="245"/>
-      <c r="AR74" s="245">
+      <c r="AR74" s="245" t="e">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS74" s="245"/>
       <c r="AT74" s="245"/>
@@ -17588,9 +17510,9 @@
       <c r="BN74" s="245"/>
       <c r="BO74" s="245"/>
       <c r="BP74" s="245"/>
-      <c r="BQ74" s="246" t="str">
+      <c r="BQ74" s="246" t="e">
         <f t="shared" si="29"/>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR74" s="246"/>
       <c r="BS74" s="246"/>
@@ -17656,9 +17578,9 @@
       <c r="CP74" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="CQ74" s="8">
+      <c r="CQ74" s="8" t="e">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR74" s="7" t="str">
         <f t="shared" si="39"/>
@@ -17668,26 +17590,26 @@
         <f t="shared" si="40"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT74" s="69">
+      <c r="CT74" s="69" t="e">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU74" s="9"/>
-      <c r="CV74" s="189">
+      <c r="CV74" s="189" t="e">
         <f t="shared" si="42"/>
-        <v>4.5755691813514673E-2</v>
-      </c>
-      <c r="CW74" s="139">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW74" s="139" t="e">
         <f t="shared" si="43"/>
-        <v>384.03120201997228</v>
-      </c>
-      <c r="CX74" s="84">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX74" s="84" t="e">
         <f t="shared" si="52"/>
-        <v>2</v>
-      </c>
-      <c r="CY74" s="87">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY74" s="87" t="e">
         <f>ROUND((CV74*CX74),4)</f>
-        <v>9.1499999999999998E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ74" s="74" t="str">
         <f t="shared" si="45"/>
@@ -17702,9 +17624,9 @@
         <v>V</v>
       </c>
       <c r="DD74" s="136"/>
-      <c r="DE74" s="141">
+      <c r="DE74" s="141" t="e">
         <f t="shared" si="53"/>
-        <v>9.1499999999999998E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF74" s="142" t="str">
         <f t="shared" si="47"/>
@@ -17743,38 +17665,32 @@
       <c r="U75" s="257"/>
       <c r="V75" s="257"/>
       <c r="W75" s="257"/>
-      <c r="X75" s="253">
-        <v>600</v>
-      </c>
+      <c r="X75" s="253"/>
       <c r="Y75" s="254"/>
       <c r="Z75" s="254"/>
       <c r="AA75" s="254"/>
       <c r="AB75" s="255"/>
-      <c r="AC75" s="253">
-        <v>600</v>
-      </c>
+      <c r="AC75" s="253"/>
       <c r="AD75" s="254"/>
       <c r="AE75" s="254"/>
       <c r="AF75" s="254"/>
       <c r="AG75" s="255"/>
-      <c r="AH75" s="253">
-        <v>600</v>
-      </c>
+      <c r="AH75" s="253"/>
       <c r="AI75" s="254"/>
       <c r="AJ75" s="254"/>
       <c r="AK75" s="254"/>
       <c r="AL75" s="255"/>
-      <c r="AM75" s="245">
+      <c r="AM75" s="245" t="e">
         <f>ROUND(AVERAGE(X75:AL75),1)</f>
-        <v>600</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN75" s="245"/>
       <c r="AO75" s="245"/>
       <c r="AP75" s="245"/>
       <c r="AQ75" s="245"/>
-      <c r="AR75" s="245">
+      <c r="AR75" s="245" t="e">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS75" s="245"/>
       <c r="AT75" s="245"/>
@@ -17807,9 +17723,9 @@
       <c r="BN75" s="245"/>
       <c r="BO75" s="245"/>
       <c r="BP75" s="245"/>
-      <c r="BQ75" s="246" t="str">
+      <c r="BQ75" s="246" t="e">
         <f t="shared" si="29"/>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR75" s="246"/>
       <c r="BS75" s="246"/>
@@ -17875,9 +17791,9 @@
       <c r="CP75" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="CQ75" s="66">
+      <c r="CQ75" s="66" t="e">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR75" s="53" t="str">
         <f t="shared" si="39"/>
@@ -17887,26 +17803,26 @@
         <f t="shared" si="40"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT75" s="70">
+      <c r="CT75" s="70" t="e">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU75" s="9"/>
-      <c r="CV75" s="190">
+      <c r="CV75" s="190" t="e">
         <f t="shared" si="42"/>
-        <v>4.5755691813514673E-2</v>
-      </c>
-      <c r="CW75" s="146">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW75" s="146" t="e">
         <f t="shared" si="43"/>
-        <v>384.03120201997228</v>
-      </c>
-      <c r="CX75" s="85">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX75" s="85" t="e">
         <f t="shared" si="52"/>
-        <v>2</v>
-      </c>
-      <c r="CY75" s="89">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY75" s="89" t="e">
         <f>ROUND((CV75*CX75),4)</f>
-        <v>9.1499999999999998E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ75" s="77" t="str">
         <f t="shared" si="45"/>
@@ -17921,9 +17837,9 @@
         <v>V</v>
       </c>
       <c r="DD75" s="136"/>
-      <c r="DE75" s="151">
+      <c r="DE75" s="151" t="e">
         <f t="shared" si="53"/>
-        <v>9.1499999999999998E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF75" s="152" t="str">
         <f t="shared" si="47"/>
@@ -18599,38 +18515,32 @@
       <c r="U81" s="257"/>
       <c r="V81" s="257"/>
       <c r="W81" s="257"/>
-      <c r="X81" s="252">
-        <v>0</v>
-      </c>
+      <c r="X81" s="252"/>
       <c r="Y81" s="252"/>
       <c r="Z81" s="252"/>
       <c r="AA81" s="252"/>
       <c r="AB81" s="252"/>
-      <c r="AC81" s="252">
-        <v>0</v>
-      </c>
+      <c r="AC81" s="252"/>
       <c r="AD81" s="252"/>
       <c r="AE81" s="252"/>
       <c r="AF81" s="252"/>
       <c r="AG81" s="252"/>
-      <c r="AH81" s="252">
-        <v>0</v>
-      </c>
+      <c r="AH81" s="252"/>
       <c r="AI81" s="252"/>
       <c r="AJ81" s="252"/>
       <c r="AK81" s="252"/>
       <c r="AL81" s="252"/>
-      <c r="AM81" s="252">
+      <c r="AM81" s="252" t="e">
         <f>ROUND(AVERAGE(X81:AL81),3)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN81" s="252"/>
       <c r="AO81" s="252"/>
       <c r="AP81" s="252"/>
       <c r="AQ81" s="252"/>
-      <c r="AR81" s="252">
+      <c r="AR81" s="252" t="e">
         <f>AM81-L81</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS81" s="252"/>
       <c r="AT81" s="252"/>
@@ -18663,9 +18573,9 @@
       <c r="BN81" s="252"/>
       <c r="BO81" s="252"/>
       <c r="BP81" s="252"/>
-      <c r="BQ81" s="246" t="str">
+      <c r="BQ81" s="246" t="e">
         <f>IF(AND(AM81&lt;=BG81,AM81&gt;=BL81),"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR81" s="246"/>
       <c r="BS81" s="246"/>
@@ -18731,9 +18641,9 @@
       <c r="CP81" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="CQ81" s="64">
+      <c r="CQ81" s="64" t="e">
         <f t="shared" ref="CQ81:CQ85" si="61">_xlfn.STDEV.P(X81:AL81)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR81" s="65" t="str">
         <f>P81</f>
@@ -18743,26 +18653,26 @@
         <f t="shared" ref="CS81:CS85" si="62">SQRT(3)</f>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT81" s="68">
+      <c r="CT81" s="68" t="e">
         <f t="shared" ref="CT81" si="63">CQ81/CS81</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU81" s="9"/>
-      <c r="CV81" s="78">
+      <c r="CV81" s="78" t="e">
         <f t="shared" ref="CV81:CV85" si="64">SQRT(SUMSQ(CT81,CN81,CH81,CB81))</f>
-        <v>2.8867517620733053E-4</v>
-      </c>
-      <c r="CW81" s="79">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW81" s="79" t="e">
         <f t="shared" ref="CW81:CW85" si="65">(CV81^4)/(((CT81^4)/2)+((CN81^4)/200)+((CH81^4)/200)+((CB81^4)/200))</f>
-        <v>200.00011531999994</v>
-      </c>
-      <c r="CX81" s="83">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX81" s="83" t="e">
         <f t="shared" ref="CX81" si="66">ROUND(TINV(0.05,CW81),0)</f>
-        <v>2</v>
-      </c>
-      <c r="CY81" s="90">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY81" s="90" t="e">
         <f>ROUND((CV81*CX81),5)</f>
-        <v>5.8E-4</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ81" s="80" t="str">
         <f>P81</f>
@@ -18777,9 +18687,9 @@
         <v>V</v>
       </c>
       <c r="DD81" s="136"/>
-      <c r="DE81" s="166">
+      <c r="DE81" s="166" t="e">
         <f>MAX(CY81:DB81)</f>
-        <v>5.8E-4</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF81" s="138" t="str">
         <f t="shared" ref="DF81:DF85" si="68">CZ81</f>
@@ -18818,38 +18728,32 @@
       <c r="U82" s="257"/>
       <c r="V82" s="257"/>
       <c r="W82" s="257"/>
-      <c r="X82" s="252">
-        <v>5</v>
-      </c>
+      <c r="X82" s="252"/>
       <c r="Y82" s="252"/>
       <c r="Z82" s="252"/>
       <c r="AA82" s="252"/>
       <c r="AB82" s="252"/>
-      <c r="AC82" s="252">
-        <v>5</v>
-      </c>
+      <c r="AC82" s="252"/>
       <c r="AD82" s="252"/>
       <c r="AE82" s="252"/>
       <c r="AF82" s="252"/>
       <c r="AG82" s="252"/>
-      <c r="AH82" s="252">
-        <v>5</v>
-      </c>
+      <c r="AH82" s="252"/>
       <c r="AI82" s="252"/>
       <c r="AJ82" s="252"/>
       <c r="AK82" s="252"/>
       <c r="AL82" s="252"/>
-      <c r="AM82" s="252">
+      <c r="AM82" s="252" t="e">
         <f>ROUND(AVERAGE(X82:AL82),3)</f>
-        <v>5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN82" s="252"/>
       <c r="AO82" s="252"/>
       <c r="AP82" s="252"/>
       <c r="AQ82" s="252"/>
-      <c r="AR82" s="252">
+      <c r="AR82" s="252" t="e">
         <f>AM82-L82</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS82" s="252"/>
       <c r="AT82" s="252"/>
@@ -18882,9 +18786,9 @@
       <c r="BN82" s="252"/>
       <c r="BO82" s="252"/>
       <c r="BP82" s="252"/>
-      <c r="BQ82" s="246" t="str">
+      <c r="BQ82" s="246" t="e">
         <f>IF(AND(AM82&lt;=BG82,AM82&gt;=BL82),"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR82" s="246"/>
       <c r="BS82" s="246"/>
@@ -18950,9 +18854,9 @@
       <c r="CP82" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="CQ82" s="8">
+      <c r="CQ82" s="8" t="e">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR82" s="7" t="str">
         <f>P82</f>
@@ -18962,26 +18866,26 @@
         <f t="shared" si="62"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT82" s="69">
+      <c r="CT82" s="69" t="e">
         <f t="shared" ref="CT82:CT85" si="71">CQ82/CS82</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU82" s="9"/>
-      <c r="CV82" s="73">
+      <c r="CV82" s="73" t="e">
         <f t="shared" si="64"/>
-        <v>2.8881539663482854E-4</v>
-      </c>
-      <c r="CW82" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW82" s="10" t="e">
         <f t="shared" si="65"/>
-        <v>200.38879963266828</v>
-      </c>
-      <c r="CX82" s="84">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX82" s="84" t="e">
         <f t="shared" ref="CX82:CX85" si="72">ROUND(TINV(0.05,CW82),0)</f>
-        <v>2</v>
-      </c>
-      <c r="CY82" s="91">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY82" s="91" t="e">
         <f>ROUND((CV82*CX82),5)</f>
-        <v>5.8E-4</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ82" s="74" t="str">
         <f>P82</f>
@@ -18996,9 +18900,9 @@
         <v>V</v>
       </c>
       <c r="DD82" s="136"/>
-      <c r="DE82" s="167">
+      <c r="DE82" s="167" t="e">
         <f t="shared" ref="DE82:DE85" si="73">MAX(CY82:DB82)</f>
-        <v>5.8E-4</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF82" s="142" t="str">
         <f t="shared" si="68"/>
@@ -19037,38 +18941,32 @@
       <c r="U83" s="257"/>
       <c r="V83" s="257"/>
       <c r="W83" s="257"/>
-      <c r="X83" s="256">
-        <v>50</v>
-      </c>
+      <c r="X83" s="256"/>
       <c r="Y83" s="256"/>
       <c r="Z83" s="256"/>
       <c r="AA83" s="256"/>
       <c r="AB83" s="256"/>
-      <c r="AC83" s="256">
-        <v>50</v>
-      </c>
+      <c r="AC83" s="256"/>
       <c r="AD83" s="256"/>
       <c r="AE83" s="256"/>
       <c r="AF83" s="256"/>
       <c r="AG83" s="256"/>
-      <c r="AH83" s="256">
-        <v>50</v>
-      </c>
+      <c r="AH83" s="256"/>
       <c r="AI83" s="256"/>
       <c r="AJ83" s="256"/>
       <c r="AK83" s="256"/>
       <c r="AL83" s="256"/>
-      <c r="AM83" s="256">
+      <c r="AM83" s="256" t="e">
         <f>ROUND(AVERAGE(X83:AL83),2)</f>
-        <v>50</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN83" s="256"/>
       <c r="AO83" s="256"/>
       <c r="AP83" s="256"/>
       <c r="AQ83" s="256"/>
-      <c r="AR83" s="256">
+      <c r="AR83" s="256" t="e">
         <f t="shared" ref="AR83:AR85" si="74">AM83-L83</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS83" s="256"/>
       <c r="AT83" s="256"/>
@@ -19101,9 +18999,9 @@
       <c r="BN83" s="256"/>
       <c r="BO83" s="256"/>
       <c r="BP83" s="256"/>
-      <c r="BQ83" s="246" t="str">
+      <c r="BQ83" s="246" t="e">
         <f>IF(AND(AM83&lt;=BG83,AM83&gt;=BL83),"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR83" s="246"/>
       <c r="BS83" s="246"/>
@@ -19169,9 +19067,9 @@
       <c r="CP83" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="CQ83" s="8">
+      <c r="CQ83" s="8" t="e">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR83" s="7" t="str">
         <f>P83</f>
@@ -19181,26 +19079,26 @@
         <f t="shared" si="62"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT83" s="69">
+      <c r="CT83" s="69" t="e">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU83" s="9"/>
-      <c r="CV83" s="73">
+      <c r="CV83" s="73" t="e">
         <f t="shared" si="64"/>
-        <v>2.8878596457122588E-3</v>
-      </c>
-      <c r="CW83" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW83" s="10" t="e">
         <f t="shared" si="65"/>
-        <v>200.30719981880611</v>
-      </c>
-      <c r="CX83" s="84">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX83" s="84" t="e">
         <f t="shared" si="72"/>
-        <v>2</v>
-      </c>
-      <c r="CY83" s="87">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY83" s="87" t="e">
         <f t="shared" ref="CY83:CY85" si="75">ROUND((CV83*CX83),4)</f>
-        <v>5.7999999999999996E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ83" s="74" t="str">
         <f>P83</f>
@@ -19215,9 +19113,9 @@
         <v>V</v>
       </c>
       <c r="DD83" s="136"/>
-      <c r="DE83" s="141">
+      <c r="DE83" s="141" t="e">
         <f t="shared" si="73"/>
-        <v>5.7999999999999996E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF83" s="142" t="str">
         <f t="shared" si="68"/>
@@ -19256,38 +19154,32 @@
       <c r="U84" s="257"/>
       <c r="V84" s="257"/>
       <c r="W84" s="257"/>
-      <c r="X84" s="245">
-        <v>600</v>
-      </c>
+      <c r="X84" s="245"/>
       <c r="Y84" s="245"/>
       <c r="Z84" s="245"/>
       <c r="AA84" s="245"/>
       <c r="AB84" s="245"/>
-      <c r="AC84" s="245">
-        <v>600</v>
-      </c>
+      <c r="AC84" s="245"/>
       <c r="AD84" s="245"/>
       <c r="AE84" s="245"/>
       <c r="AF84" s="245"/>
       <c r="AG84" s="245"/>
-      <c r="AH84" s="245">
-        <v>600</v>
-      </c>
+      <c r="AH84" s="245"/>
       <c r="AI84" s="245"/>
       <c r="AJ84" s="245"/>
       <c r="AK84" s="245"/>
       <c r="AL84" s="245"/>
-      <c r="AM84" s="245">
+      <c r="AM84" s="245" t="e">
         <f>ROUND(AVERAGE(X84:AL84),1)</f>
-        <v>600</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN84" s="245"/>
       <c r="AO84" s="245"/>
       <c r="AP84" s="245"/>
       <c r="AQ84" s="245"/>
-      <c r="AR84" s="245">
+      <c r="AR84" s="245" t="e">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS84" s="245"/>
       <c r="AT84" s="245"/>
@@ -19320,9 +19212,9 @@
       <c r="BN84" s="245"/>
       <c r="BO84" s="245"/>
       <c r="BP84" s="245"/>
-      <c r="BQ84" s="246" t="str">
+      <c r="BQ84" s="246" t="e">
         <f>IF(AND(AM84&lt;=BG84,AM84&gt;=BL84),"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR84" s="246"/>
       <c r="BS84" s="246"/>
@@ -19388,9 +19280,9 @@
       <c r="CP84" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="CQ84" s="8">
+      <c r="CQ84" s="8" t="e">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR84" s="7" t="str">
         <f>P84</f>
@@ -19400,26 +19292,26 @@
         <f t="shared" si="62"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT84" s="69">
+      <c r="CT84" s="69" t="e">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU84" s="9"/>
-      <c r="CV84" s="73">
+      <c r="CV84" s="73" t="e">
         <f t="shared" si="64"/>
-        <v>2.8914630091587432E-2</v>
-      </c>
-      <c r="CW84" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW84" s="10" t="e">
         <f t="shared" si="65"/>
-        <v>201.3067860522948</v>
-      </c>
-      <c r="CX84" s="84">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX84" s="84" t="e">
         <f t="shared" si="72"/>
-        <v>2</v>
-      </c>
-      <c r="CY84" s="87">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY84" s="87" t="e">
         <f t="shared" si="75"/>
-        <v>5.7799999999999997E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ84" s="74" t="str">
         <f>P84</f>
@@ -19434,9 +19326,9 @@
         <v>V</v>
       </c>
       <c r="DD84" s="136"/>
-      <c r="DE84" s="141">
+      <c r="DE84" s="141" t="e">
         <f t="shared" si="73"/>
-        <v>5.7799999999999997E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF84" s="142" t="str">
         <f t="shared" si="68"/>
@@ -19475,38 +19367,32 @@
       <c r="U85" s="257"/>
       <c r="V85" s="257"/>
       <c r="W85" s="257"/>
-      <c r="X85" s="245">
-        <v>-600</v>
-      </c>
+      <c r="X85" s="245"/>
       <c r="Y85" s="245"/>
       <c r="Z85" s="245"/>
       <c r="AA85" s="245"/>
       <c r="AB85" s="245"/>
-      <c r="AC85" s="245">
-        <v>-600</v>
-      </c>
+      <c r="AC85" s="245"/>
       <c r="AD85" s="245"/>
       <c r="AE85" s="245"/>
       <c r="AF85" s="245"/>
       <c r="AG85" s="245"/>
-      <c r="AH85" s="245">
-        <v>-600</v>
-      </c>
+      <c r="AH85" s="245"/>
       <c r="AI85" s="245"/>
       <c r="AJ85" s="245"/>
       <c r="AK85" s="245"/>
       <c r="AL85" s="245"/>
-      <c r="AM85" s="245">
+      <c r="AM85" s="245" t="e">
         <f>ROUND(AVERAGE(X85:AL85),1)</f>
-        <v>-600</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN85" s="245"/>
       <c r="AO85" s="245"/>
       <c r="AP85" s="245"/>
       <c r="AQ85" s="245"/>
-      <c r="AR85" s="245">
+      <c r="AR85" s="245" t="e">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS85" s="245"/>
       <c r="AT85" s="245"/>
@@ -19539,9 +19425,9 @@
       <c r="BN85" s="245"/>
       <c r="BO85" s="245"/>
       <c r="BP85" s="245"/>
-      <c r="BQ85" s="246" t="str">
+      <c r="BQ85" s="246" t="e">
         <f>IF(AND(AM85&lt;=BG85,AM85&gt;=BL85),"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR85" s="246"/>
       <c r="BS85" s="246"/>
@@ -19607,9 +19493,9 @@
       <c r="CP85" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="CQ85" s="66">
+      <c r="CQ85" s="66" t="e">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR85" s="53" t="str">
         <f>P85</f>
@@ -19619,26 +19505,26 @@
         <f t="shared" si="62"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT85" s="70">
+      <c r="CT85" s="70" t="e">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU85" s="9"/>
-      <c r="CV85" s="75">
+      <c r="CV85" s="75" t="e">
         <f t="shared" si="64"/>
-        <v>2.8914630091587432E-2</v>
-      </c>
-      <c r="CW85" s="76">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW85" s="76" t="e">
         <f t="shared" si="65"/>
-        <v>201.3067860522948</v>
-      </c>
-      <c r="CX85" s="85">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX85" s="85" t="e">
         <f t="shared" si="72"/>
-        <v>2</v>
-      </c>
-      <c r="CY85" s="89">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY85" s="89" t="e">
         <f t="shared" si="75"/>
-        <v>5.7799999999999997E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ85" s="77" t="str">
         <f>P85</f>
@@ -19653,9 +19539,9 @@
         <v>V</v>
       </c>
       <c r="DD85" s="136"/>
-      <c r="DE85" s="151">
+      <c r="DE85" s="151" t="e">
         <f t="shared" si="73"/>
-        <v>5.7799999999999997E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF85" s="152" t="str">
         <f t="shared" si="68"/>
@@ -21182,38 +21068,32 @@
       <c r="U96" s="257"/>
       <c r="V96" s="257"/>
       <c r="W96" s="257"/>
-      <c r="X96" s="245">
-        <v>10</v>
-      </c>
+      <c r="X96" s="245"/>
       <c r="Y96" s="245"/>
       <c r="Z96" s="245"/>
       <c r="AA96" s="245"/>
       <c r="AB96" s="245"/>
-      <c r="AC96" s="245">
-        <v>10</v>
-      </c>
+      <c r="AC96" s="245"/>
       <c r="AD96" s="245"/>
       <c r="AE96" s="245"/>
       <c r="AF96" s="245"/>
       <c r="AG96" s="245"/>
-      <c r="AH96" s="245">
-        <v>10</v>
-      </c>
+      <c r="AH96" s="245"/>
       <c r="AI96" s="245"/>
       <c r="AJ96" s="245"/>
       <c r="AK96" s="245"/>
       <c r="AL96" s="245"/>
-      <c r="AM96" s="245">
+      <c r="AM96" s="245" t="e">
         <f>ROUND(AVERAGE(X96:AL96),1)</f>
-        <v>10</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN96" s="245"/>
       <c r="AO96" s="245"/>
       <c r="AP96" s="245"/>
       <c r="AQ96" s="245"/>
-      <c r="AR96" s="245">
+      <c r="AR96" s="245" t="e">
         <f t="shared" ref="AR96:AR97" si="92">AM96-L96</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS96" s="245"/>
       <c r="AT96" s="245"/>
@@ -21246,9 +21126,9 @@
       <c r="BN96" s="245"/>
       <c r="BO96" s="245"/>
       <c r="BP96" s="245"/>
-      <c r="BQ96" s="246" t="str">
+      <c r="BQ96" s="246" t="e">
         <f>IF(AND(AM96&lt;=BG96,AM96&gt;=BL96),"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR96" s="246"/>
       <c r="BS96" s="246"/>
@@ -21314,9 +21194,9 @@
       <c r="CP96" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="CQ96" s="64">
+      <c r="CQ96" s="64" t="e">
         <f t="shared" ref="CQ96:CQ97" si="99">_xlfn.STDEV.P(X96:AL96)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR96" s="65" t="str">
         <f>P96</f>
@@ -21326,26 +21206,26 @@
         <f t="shared" ref="CS96:CS97" si="100">SQRT(3)</f>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT96" s="72">
+      <c r="CT96" s="72" t="e">
         <f t="shared" ref="CT96:CT97" si="101">CQ96/CS96</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU96" s="9"/>
-      <c r="CV96" s="78">
+      <c r="CV96" s="78" t="e">
         <f t="shared" ref="CV96:CV97" si="102">SQRT(SUMSQ(CT96,CN96,CH96,CB96))</f>
-        <v>2.8870080677638112E-2</v>
-      </c>
-      <c r="CW96" s="79">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW96" s="79" t="e">
         <f t="shared" ref="CW96:CW97" si="103">(CV96^4)/(((CT96^4)/2)+((CN96^4)/200)+((CH96^4)/200)+((CB96^4)/200))</f>
-        <v>200.07114799774902</v>
-      </c>
-      <c r="CX96" s="83">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX96" s="83" t="e">
         <f t="shared" ref="CX96:CX97" si="104">ROUND(TINV(0.05,CW96),0)</f>
-        <v>2</v>
-      </c>
-      <c r="CY96" s="92">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY96" s="92" t="e">
         <f>ROUND((CV96*CX96),3)</f>
-        <v>5.8000000000000003E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ96" s="80" t="str">
         <f>P96</f>
@@ -21360,9 +21240,9 @@
         <v>mV</v>
       </c>
       <c r="DD96" s="136"/>
-      <c r="DE96" s="137">
+      <c r="DE96" s="137" t="e">
         <f>MAX(CY96:DB96)</f>
-        <v>5.8000000000000003E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF96" s="138" t="str">
         <f t="shared" ref="DF96:DF97" si="106">CZ96</f>
@@ -21401,38 +21281,32 @@
       <c r="U97" s="257"/>
       <c r="V97" s="257"/>
       <c r="W97" s="257"/>
-      <c r="X97" s="245">
-        <v>600</v>
-      </c>
+      <c r="X97" s="245"/>
       <c r="Y97" s="245"/>
       <c r="Z97" s="245"/>
       <c r="AA97" s="245"/>
       <c r="AB97" s="245"/>
-      <c r="AC97" s="245">
-        <v>600</v>
-      </c>
+      <c r="AC97" s="245"/>
       <c r="AD97" s="245"/>
       <c r="AE97" s="245"/>
       <c r="AF97" s="245"/>
       <c r="AG97" s="245"/>
-      <c r="AH97" s="245">
-        <v>600</v>
-      </c>
+      <c r="AH97" s="245"/>
       <c r="AI97" s="245"/>
       <c r="AJ97" s="245"/>
       <c r="AK97" s="245"/>
       <c r="AL97" s="245"/>
-      <c r="AM97" s="245">
+      <c r="AM97" s="245" t="e">
         <f>ROUND(AVERAGE(X97:AL97),1)</f>
-        <v>600</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN97" s="245"/>
       <c r="AO97" s="245"/>
       <c r="AP97" s="245"/>
       <c r="AQ97" s="245"/>
-      <c r="AR97" s="245">
+      <c r="AR97" s="245" t="e">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS97" s="245"/>
       <c r="AT97" s="245"/>
@@ -21465,9 +21339,9 @@
       <c r="BN97" s="245"/>
       <c r="BO97" s="245"/>
       <c r="BP97" s="245"/>
-      <c r="BQ97" s="246" t="str">
+      <c r="BQ97" s="246" t="e">
         <f>IF(AND(AM97&lt;=BG97,AM97&gt;=BL97),"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR97" s="246"/>
       <c r="BS97" s="246"/>
@@ -21533,9 +21407,9 @@
       <c r="CP97" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="CQ97" s="66">
+      <c r="CQ97" s="66" t="e">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR97" s="53" t="str">
         <f>P97</f>
@@ -21545,26 +21419,26 @@
         <f t="shared" si="100"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT97" s="71">
+      <c r="CT97" s="71" t="e">
         <f t="shared" si="101"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU97" s="9"/>
-      <c r="CV97" s="75">
+      <c r="CV97" s="75" t="e">
         <f t="shared" si="102"/>
-        <v>2.8886603007853544E-2</v>
-      </c>
-      <c r="CW97" s="76">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW97" s="76" t="e">
         <f t="shared" si="103"/>
-        <v>200.52919907372751</v>
-      </c>
-      <c r="CX97" s="85">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX97" s="85" t="e">
         <f t="shared" si="104"/>
-        <v>2</v>
-      </c>
-      <c r="CY97" s="93">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY97" s="93" t="e">
         <f t="shared" ref="CY97" si="107">ROUND((CV97*CX97),3)</f>
-        <v>5.8000000000000003E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ97" s="77" t="str">
         <f>P97</f>
@@ -21579,9 +21453,9 @@
         <v>mV</v>
       </c>
       <c r="DD97" s="136"/>
-      <c r="DE97" s="151">
+      <c r="DE97" s="151" t="e">
         <f>MAX(CY97:DB97)</f>
-        <v>5.8000000000000003E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF97" s="152" t="str">
         <f t="shared" si="106"/>
@@ -22145,9 +22019,7 @@
       <c r="U102" s="257"/>
       <c r="V102" s="257"/>
       <c r="W102" s="257"/>
-      <c r="X102" s="245">
-        <v>0.5</v>
-      </c>
+      <c r="X102" s="245"/>
       <c r="Y102" s="245"/>
       <c r="Z102" s="245"/>
       <c r="AA102" s="245"/>
@@ -22162,17 +22034,17 @@
       <c r="AJ102" s="245"/>
       <c r="AK102" s="245"/>
       <c r="AL102" s="245"/>
-      <c r="AM102" s="367">
+      <c r="AM102" s="367" t="e">
         <f t="shared" ref="AM102:AM104" si="108">AVERAGE(X102:AL102)</f>
-        <v>0.5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN102" s="245"/>
       <c r="AO102" s="245"/>
       <c r="AP102" s="245"/>
       <c r="AQ102" s="245"/>
-      <c r="AR102" s="245">
+      <c r="AR102" s="245" t="e">
         <f>AM102-L102</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS102" s="245"/>
       <c r="AT102" s="245"/>
@@ -22205,9 +22077,9 @@
       <c r="BN102" s="245"/>
       <c r="BO102" s="245"/>
       <c r="BP102" s="245"/>
-      <c r="BQ102" s="246" t="str">
+      <c r="BQ102" s="246" t="e">
         <f>IF(AND(AM102&lt;=BG102,AM102&gt;=BL102),"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR102" s="246"/>
       <c r="BS102" s="246"/>
@@ -22273,9 +22145,9 @@
       <c r="CP102" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="CQ102" s="64">
+      <c r="CQ102" s="64" t="e">
         <f t="shared" ref="CQ102:CQ104" si="115">_xlfn.STDEV.P(X102:AL102)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR102" s="65" t="str">
         <f>P102</f>
@@ -22285,26 +22157,26 @@
         <f t="shared" ref="CS102:CS104" si="116">SQRT(3)</f>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT102" s="68">
+      <c r="CT102" s="68" t="e">
         <f t="shared" ref="CT102:CT104" si="117">CQ102/CS102</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU102" s="9"/>
-      <c r="CV102" s="78">
+      <c r="CV102" s="78" t="e">
         <f t="shared" ref="CV102:CV104" si="118">SQRT(SUMSQ(CT102,CN102,CH102,CB102))</f>
-        <v>2.8871099014989601E-2</v>
-      </c>
-      <c r="CW102" s="79">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW102" s="79" t="e">
         <f t="shared" ref="CW102:CW104" si="119">(CV102^4)/(((CT102^4)/2)+((CN102^4)/200)+((CH102^4)/200)+((CB102^4)/200))</f>
-        <v>200.09937199386704</v>
-      </c>
-      <c r="CX102" s="83">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX102" s="83" t="e">
         <f t="shared" ref="CX102:CX104" si="120">ROUND(TINV(0.05,CW102),0)</f>
-        <v>2</v>
-      </c>
-      <c r="CY102" s="94">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY102" s="94" t="e">
         <f>(CV102*CX102)</f>
-        <v>5.7742198029979201E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ102" s="80" t="str">
         <f>P102</f>
@@ -22319,9 +22191,9 @@
         <v>V</v>
       </c>
       <c r="DD102" s="136"/>
-      <c r="DE102" s="137">
+      <c r="DE102" s="137" t="e">
         <f>MAX(CY102:DB102)</f>
-        <v>5.7742198029979201E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF102" s="138" t="str">
         <f t="shared" ref="DF102:DF104" si="122">CZ102</f>
@@ -22360,9 +22232,7 @@
       <c r="U103" s="257"/>
       <c r="V103" s="257"/>
       <c r="W103" s="257"/>
-      <c r="X103" s="245">
-        <v>0.5</v>
-      </c>
+      <c r="X103" s="245"/>
       <c r="Y103" s="245"/>
       <c r="Z103" s="245"/>
       <c r="AA103" s="245"/>
@@ -22377,17 +22247,17 @@
       <c r="AJ103" s="245"/>
       <c r="AK103" s="245"/>
       <c r="AL103" s="245"/>
-      <c r="AM103" s="367">
+      <c r="AM103" s="367" t="e">
         <f t="shared" si="108"/>
-        <v>0.5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN103" s="245"/>
       <c r="AO103" s="245"/>
       <c r="AP103" s="245"/>
       <c r="AQ103" s="245"/>
-      <c r="AR103" s="245">
+      <c r="AR103" s="245" t="e">
         <f>AM103-L103</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS103" s="245"/>
       <c r="AT103" s="245"/>
@@ -22420,9 +22290,9 @@
       <c r="BN103" s="245"/>
       <c r="BO103" s="245"/>
       <c r="BP103" s="245"/>
-      <c r="BQ103" s="246" t="str">
+      <c r="BQ103" s="246" t="e">
         <f>IF(AND(AM103&lt;=BG103,AM103&gt;=BL103),"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR103" s="246"/>
       <c r="BS103" s="246"/>
@@ -22488,9 +22358,9 @@
       <c r="CP103" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="CQ103" s="8">
+      <c r="CQ103" s="8" t="e">
         <f t="shared" si="115"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR103" s="7" t="str">
         <f>P103</f>
@@ -22500,26 +22370,26 @@
         <f t="shared" si="116"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT103" s="69">
+      <c r="CT103" s="69" t="e">
         <f t="shared" si="117"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU103" s="9"/>
-      <c r="CV103" s="73">
+      <c r="CV103" s="73" t="e">
         <f t="shared" si="118"/>
-        <v>2.8867513478577151E-2</v>
-      </c>
-      <c r="CW103" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW103" s="10" t="e">
         <f t="shared" si="119"/>
-        <v>200.00000052920004</v>
-      </c>
-      <c r="CX103" s="84">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX103" s="84" t="e">
         <f t="shared" si="120"/>
-        <v>2</v>
-      </c>
-      <c r="CY103" s="95">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY103" s="95" t="e">
         <f>(CV103*CX103)</f>
-        <v>5.7735026957154302E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ103" s="74" t="str">
         <f>P103</f>
@@ -22534,9 +22404,9 @@
         <v>V</v>
       </c>
       <c r="DD103" s="136"/>
-      <c r="DE103" s="141">
+      <c r="DE103" s="141" t="e">
         <f t="shared" ref="DE103:DE104" si="123">MAX(CY103:DB103)</f>
-        <v>5.7735026957154302E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF103" s="142" t="str">
         <f t="shared" si="122"/>
@@ -22575,9 +22445,7 @@
       <c r="U104" s="257"/>
       <c r="V104" s="257"/>
       <c r="W104" s="257"/>
-      <c r="X104" s="245">
-        <v>500</v>
-      </c>
+      <c r="X104" s="245"/>
       <c r="Y104" s="245"/>
       <c r="Z104" s="245"/>
       <c r="AA104" s="245"/>
@@ -22592,17 +22460,17 @@
       <c r="AJ104" s="245"/>
       <c r="AK104" s="245"/>
       <c r="AL104" s="245"/>
-      <c r="AM104" s="367">
+      <c r="AM104" s="367" t="e">
         <f t="shared" si="108"/>
-        <v>500</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AN104" s="245"/>
       <c r="AO104" s="245"/>
       <c r="AP104" s="245"/>
       <c r="AQ104" s="245"/>
-      <c r="AR104" s="245">
+      <c r="AR104" s="245" t="e">
         <f>AM104-L104</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AS104" s="245"/>
       <c r="AT104" s="245"/>
@@ -22635,9 +22503,9 @@
       <c r="BN104" s="245"/>
       <c r="BO104" s="245"/>
       <c r="BP104" s="245"/>
-      <c r="BQ104" s="246" t="str">
+      <c r="BQ104" s="246" t="e">
         <f>IF(AND(AM104&lt;=BG104,AM104&gt;=BL104),"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="BR104" s="246"/>
       <c r="BS104" s="246"/>
@@ -22703,9 +22571,9 @@
       <c r="CP104" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="CQ104" s="66">
+      <c r="CQ104" s="66" t="e">
         <f t="shared" si="115"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CR104" s="53" t="str">
         <f>P104</f>
@@ -22715,26 +22583,26 @@
         <f t="shared" si="116"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT104" s="70">
+      <c r="CT104" s="70" t="e">
         <f t="shared" si="117"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CU104" s="9"/>
-      <c r="CV104" s="75">
+      <c r="CV104" s="75" t="e">
         <f t="shared" si="118"/>
-        <v>4.5755691813514673E-2</v>
-      </c>
-      <c r="CW104" s="76">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CW104" s="76" t="e">
         <f t="shared" si="119"/>
-        <v>384.03120201997228</v>
-      </c>
-      <c r="CX104" s="85">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CX104" s="85" t="e">
         <f t="shared" si="120"/>
-        <v>2</v>
-      </c>
-      <c r="CY104" s="96">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="CY104" s="96" t="e">
         <f>(CV104*CX104)</f>
-        <v>9.1511383627029347E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="CZ104" s="77" t="str">
         <f>P104</f>
@@ -22749,9 +22617,9 @@
         <v>V</v>
       </c>
       <c r="DD104" s="136"/>
-      <c r="DE104" s="151">
+      <c r="DE104" s="151" t="e">
         <f t="shared" si="123"/>
-        <v>9.1511383627029347E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="DF104" s="152" t="str">
         <f t="shared" si="122"/>
@@ -25083,11 +24951,14 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0.39370078740157483" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="85" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="85" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;L&amp;8Page &amp;P of &amp;N&amp;R&amp;8 7F-04-02 Rev. 02
 Effectivity Date: August 01 ,2019</oddFooter>
   </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="76" min="1" max="51" man="1"/>
+  </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
